--- a/ReBike_BusinessRules_Template.xlsx
+++ b/ReBike_BusinessRules_Template.xlsx
@@ -1216,7 +1216,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="24" xml:space="preserve">
+    <row r="24">
       <c r="A24" t="str">
         <v>BR-SHIP-05</v>
       </c>
@@ -1226,8 +1226,8 @@
       <c r="C24" t="str">
         <v>Cancellation Restriction After Shipping</v>
       </c>
-      <c r="D24" t="str" xml:space="preserve">
-        <v xml:space="preserve">Khi đơn hàng đã sang các bước SELLER_SHIPPED / AT_WAREHOUSE_PENDING_ADMIN / RE_INSPECTION / SHIPPING, việc hủy không còn là thao tác self-service đơn giản của Buyer. Mọi xử lý tiếp theo phải theo chính sách vận hành và hoàn tiền của hệ thống.</v>
+      <c r="D24" t="str">
+        <v>Khi đơn hàng đã sang các bước SELLER_SHIPPED / AT_WAREHOUSE_PENDING_ADMIN / RE_INSPECTION / SHIPPING, việc hủy không còn là thao tác self-service đơn giản của Buyer. Mọi xử lý tiếp theo phải theo chính sách vận hành và hoàn tiền của hệ thống.</v>
       </c>
       <c r="E24" t="str">
         <v>Buyer / Admin / System</v>
@@ -1786,7 +1786,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="41" xml:space="preserve">
+    <row r="41">
       <c r="A41" t="str">
         <v>DR-BUYER-05</v>
       </c>
@@ -1796,8 +1796,8 @@
       <c r="C41" t="str">
         <v>BUYER.Phone Number</v>
       </c>
-      <c r="D41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Có thể để trống tùy scope. Nếu được khai báo thì phải là số điện thoại hợp lệ theo chuẩn hệ thống và không chứa ký tự không hợp lệ.</v>
+      <c r="D41" t="str">
+        <v>Có thể để trống tùy scope. Nếu được khai báo thì phải là số điện thoại hợp lệ theo chuẩn hệ thống và không chứa ký tự không hợp lệ.</v>
       </c>
       <c r="E41" t="str">
         <v>System</v>
@@ -3653,7 +3653,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="94" xml:space="preserve">
+    <row r="94">
       <c r="A94" t="str">
         <v>BR-REV-04</v>
       </c>
@@ -3663,8 +3663,8 @@
       <c r="C94" t="str">
         <v>Seller Reputation Aggregation</v>
       </c>
-      <c r="D94" t="str" xml:space="preserve">
-        <v xml:space="preserve">Điểm uy tín của Seller được tổng hợp từ các review hợp lệ của các giao dịch thành công. Seller Dashboard hiển thị tổng số review, điểm trung bình và tỷ lệ phản hồi tích cực.</v>
+      <c r="D94" t="str">
+        <v>Điểm uy tín của Seller được tổng hợp từ các review hợp lệ của các giao dịch thành công. Seller Dashboard hiển thị tổng số review, điểm trung bình và tỷ lệ phản hồi tích cực.</v>
       </c>
       <c r="E94" t="str">
         <v>System / Seller</v>
@@ -3685,7 +3685,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
+    <row r="95">
       <c r="A95" t="str">
         <v>BR-ADMIN-01</v>
       </c>
@@ -3695,8 +3695,8 @@
       <c r="C95" t="str">
         <v>Category Management</v>
       </c>
-      <c r="D95" t="str" xml:space="preserve">
-        <v xml:space="preserve">Admin có thể tạo, cập nhật và quản lý danh mục / brand category dùng trong hệ thống. Category không còn hiệu lực sẽ không được dùng cho dữ liệu mới.</v>
+      <c r="D95" t="str">
+        <v>Admin có thể tạo, cập nhật và quản lý danh mục / brand category dùng trong hệ thống. Category không còn hiệu lực sẽ không được dùng cho dữ liệu mới.</v>
       </c>
       <c r="E95" t="str">
         <v>Admin</v>
@@ -3717,7 +3717,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="96" xml:space="preserve">
+    <row r="96">
       <c r="A96" t="str">
         <v>BR-ADMIN-02</v>
       </c>
@@ -3727,8 +3727,8 @@
       <c r="C96" t="str">
         <v>Transaction Fee Configuration and History</v>
       </c>
-      <c r="D96" t="str" xml:space="preserve">
-        <v xml:space="preserve">Admin có thể cấu hình mức phí giao dịch và xem lịch sử giao dịch trong Admin Dashboard. Mọi thay đổi cấu hình phí phải được lưu lại để đối soát và theo dõi.</v>
+      <c r="D96" t="str">
+        <v>Admin có thể cấu hình mức phí giao dịch và xem lịch sử giao dịch trong Admin Dashboard. Mọi thay đổi cấu hình phí phải được lưu lại để đối soát và theo dõi.</v>
       </c>
       <c r="E96" t="str">
         <v>Admin / System</v>
@@ -3749,7 +3749,7 @@
         <v>Current app flow</v>
       </c>
     </row>
-    <row r="97" xml:space="preserve">
+    <row r="97">
       <c r="A97" t="str">
         <v>BR-SELL-01</v>
       </c>
@@ -3759,8 +3759,8 @@
       <c r="C97" t="str">
         <v>Orders and Deposits Visibility</v>
       </c>
-      <c r="D97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Seller Dashboard hiển thị danh sách Orders / Deposits liên quan đến Seller hiện tại. Dữ liệu được lấy từ API; nếu API chưa sẵn sàng có thể dùng dữ liệu fallback / mock để hiển thị.</v>
+      <c r="D97" t="str">
+        <v>Seller Dashboard hiển thị danh sách Orders / Deposits liên quan đến Seller hiện tại. Dữ liệu được lấy từ API; nếu API chưa sẵn sàng có thể dùng dữ liệu fallback / mock để hiển thị.</v>
       </c>
       <c r="E97" t="str">
         <v>Seller / System</v>
@@ -3779,6 +3779,486 @@
       </c>
       <c r="J97" t="str">
         <v>Current app flow</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>BR-PAY-VQR-01</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Mã đơn hàng</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Mỗi đơn VietQR (SQLite) có orderCode duy nhất dạng ORDyyyyMMddxxx; sequence tăng theo ngày (xxx 3 số).</v>
+      </c>
+      <c r="E98" t="str">
+        <v>System</v>
+      </c>
+      <c r="F98" t="str">
+        <v>POST /api/vietqr/orders</v>
+      </c>
+      <c r="G98" t="str">
+        <v>Buyer gửi amount ≥ 1000 VND</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Tạo bản ghi orders.status = CREATED; không trùng order_code</v>
+      </c>
+      <c r="I98" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J98" t="str">
+        <v>docs/VIETQR-MODULE.md; backend/src/vietqr</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>BR-PAY-VQR-02</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Mã thanh toán</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Mỗi lần sinh QR tạo payment_code duy nhất dạng PAYyyyyMMddxxx.</v>
+      </c>
+      <c r="E99" t="str">
+        <v>System</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Tạo payment + gọi VietQR API</v>
+      </c>
+      <c r="G99" t="str">
+        <v>Cần order hợp lệ và không vi phạm rule chặn QR song song</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Lưu payments.payment_code UNIQUE</v>
+      </c>
+      <c r="I99" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J99" t="str">
+        <v>vietqr/repositories/paymentRepository.js</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>BR-PAY-VQR-03</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Nội dung chuyển khoản</v>
+      </c>
+      <c r="D100" t="str">
+        <v>transferContent = TT_&lt;orderCode&gt;; chuẩn hóa ký tự theo VietQR; độ dài addInfo tối đa 25 ký tự.</v>
+      </c>
+      <c r="E100" t="str">
+        <v>System</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Gọi api.vietqr.io/v2/generate</v>
+      </c>
+      <c r="G100" t="str">
+        <v>Chuẩn bị payload amount, addInfo</v>
+      </c>
+      <c r="H100" t="str">
+        <v>normalizeAddInfo + cắt chuỗi trước khi gửi API</v>
+      </c>
+      <c r="I100" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J100" t="str">
+        <v>vietqr/utils/normalizeVietQrText.js</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>BR-PAY-VQR-04</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Cấu hình bảo mật</v>
+      </c>
+      <c r="D101" t="str">
+        <v>CLIENT_ID, API_KEY, STK, tên TK, acqId chỉ đọc từ biến môi trường (.env); cấm hardcode trong source.</v>
+      </c>
+      <c r="E101" t="str">
+        <v>System / DevOps</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Khởi động server / gọi VietQR</v>
+      </c>
+      <c r="G101" t="str">
+        <v>Thiếu biến bắt buộc</v>
+      </c>
+      <c r="H101" t="str">
+        <v>API trả 503 VIETQR_NOT_CONFIGURED; không gọi VietQR</v>
+      </c>
+      <c r="I101" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J101" t="str">
+        <v>backend/.env.example; loadVietQrConfig.js</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>BR-PAY-VQR-05</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Trạng thái đơn (SQLite)</v>
+      </c>
+      <c r="D102" t="str">
+        <v>orders.status: CREATED → AWAITING_PAYMENT (sau khi có payment PENDING hợp lệ) → PAID (xác nhận thành công) hoặc CANCELLED.</v>
+      </c>
+      <c r="E102" t="str">
+        <v>System</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Luồng thanh toán VietQR</v>
+      </c>
+      <c r="G102" t="str">
+        <v>Theo sự kiện tạo QR / simulate / hủy (nếu có)</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Cập nhật orders + paid_at khi PAID</v>
+      </c>
+      <c r="I102" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J102" t="str">
+        <v>vietQrPaymentFlowService.js</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>BR-PAY-VQR-06</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Trạng thái thanh toán</v>
+      </c>
+      <c r="D103" t="str">
+        <v>payments.status: PENDING (chờ CK) | SUCCESS | FAILED (API lỗi) | EXPIRED (quá expired_at).</v>
+      </c>
+      <c r="E103" t="str">
+        <v>System</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Sau generate / hết hạn / admin simulate</v>
+      </c>
+      <c r="G103" t="str">
+        <v>Theo thời gian và kết quả API</v>
+      </c>
+      <c r="H103" t="str">
+        <v>expireStalePendingPayments đánh dấu EXPIRED khi quá hạn</v>
+      </c>
+      <c r="I103" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J103" t="str">
+        <v>paymentRepository.js</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>BR-PAY-VQR-07</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Thời hạn QR</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Thời gian sống QR cấu hình VIETQR_QR_TTL_MINUTES (mặc định 15 phút); lưu expired_at; UI countdown.</v>
+      </c>
+      <c r="E104" t="str">
+        <v>System / Buyer</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Hiển thị QR</v>
+      </c>
+      <c r="G104" t="str">
+        <v>now &lt; expired_at</v>
+      </c>
+      <c r="H104" t="str">
+        <v>PENDING hợp lệ; hết hạn chuyển EXPIRED khi đồng bộ</v>
+      </c>
+      <c r="I104" t="str">
+        <v>SHOULD</v>
+      </c>
+      <c r="J104" t="str">
+        <v>VIETQR-MODULE.md; VietQrCheckoutPage.tsx</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>BR-PAY-VQR-08</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Chống trùng QR hiệu lực</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Không tạo payment/QR mới nếu đã có payment PENDING cùng order và chưa hết expired_at.</v>
+      </c>
+      <c r="E105" t="str">
+        <v>System</v>
+      </c>
+      <c r="F105" t="str">
+        <v>POST .../payments/qr</v>
+      </c>
+      <c r="G105" t="str">
+        <v>Latest payment PENDING và còn hạn</v>
+      </c>
+      <c r="H105" t="str">
+        <v>400 QR_STILL_VALID — yêu cầu chờ hết hạn hoặc regenerate có điều kiện</v>
+      </c>
+      <c r="I105" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J105" t="str">
+        <v>vietQrPaymentFlowService.js</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>BR-PAY-VQR-09</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Tạo lại QR</v>
+      </c>
+      <c r="D106" t="str">
+        <v>POST .../payments/regenerate: chỉ khi QR hiện tại không còn PENDING hợp lệ; có thể đánh dấu PENDING quá hạn → EXPIRED trước khi tạo mới.</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Buyer</v>
+      </c>
+      <c r="F106" t="str">
+        <v>User bấm Tạo lại QR</v>
+      </c>
+      <c r="G106" t="str">
+        <v>QR hết hạn hoặc đã EXPIRED/FAILED</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Tạo payment mới + gọi lại VietQR</v>
+      </c>
+      <c r="I106" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J106" t="str">
+        <v>vietQrPaymentFlowService.regenerateQrForOrder</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>BR-PAY-VQR-10</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Audit payment_logs</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Mọi lần generate thành công / từ chối API / lỗi mạng phải ghi payment_logs (action, request_data, response_data, note).</v>
+      </c>
+      <c r="E107" t="str">
+        <v>System</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Gọi VietQR &amp; cập nhật payment</v>
+      </c>
+      <c r="G107" t="str">
+        <v>Luôn sau khi có payment_id</v>
+      </c>
+      <c r="H107" t="str">
+        <v>INSERT payment_logs liên kết payment_id</v>
+      </c>
+      <c r="I107" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J107" t="str">
+        <v>paymentLogRepository.js</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>BR-PAY-VQR-11</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Xác nhận thanh toán (demo)</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Admin POST .../simulate-success: chỉ từ PENDING → SUCCESS và order → PAID; dùng cho đồ án — production thay bằng webhook/IPN ngân hàng.</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Đối soát demo / báo cáo</v>
+      </c>
+      <c r="G108" t="str">
+        <v>payment.status = PENDING</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Cập nhật paidAt; ghi log ADMIN_SIMULATE_SUCCESS</v>
+      </c>
+      <c r="I108" t="str">
+        <v>MUST (scope demo)</v>
+      </c>
+      <c r="J108" t="str">
+        <v>vietQrAdminController.js</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>BR-PAY-VQR-12</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Phân quyền &amp; sở hữu đơn</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Buyer chỉ đọc/tạo QR cho đơn có buyer_ref trùng JWT user id; Admin xem toàn bộ payment &amp; log.</v>
+      </c>
+      <c r="E109" t="str">
+        <v>System</v>
+      </c>
+      <c r="F109" t="str">
+        <v>GET order / payment</v>
+      </c>
+      <c r="G109" t="str">
+        <v>So khớp buyer_ref</v>
+      </c>
+      <c r="H109" t="str">
+        <v>403 FORBIDDEN nếu không phải chủ đơn</v>
+      </c>
+      <c r="I109" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J109" t="str">
+        <v>vietQrController.js; auth middleware</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>BR-PAY-VQR-13</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Payments (VietQR)</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Tách dữ liệu</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Đơn VietQR lưu SQLite (file vietqr.sqlite), tách khỏi Order MongoDB của ShopBike — không đồng bộ tự động với đơn mua xe chính.</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Architect</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Thiết kế module đồ án</v>
+      </c>
+      <c r="G110" t="str">
+        <v>Luồng VietQR độc lập</v>
+      </c>
+      <c r="H110" t="str">
+        <v>API prefix /api/vietqr</v>
+      </c>
+      <c r="I110" t="str">
+        <v>INFO</v>
+      </c>
+      <c r="J110" t="str">
+        <v>docs/VIETQR-MODULE.md</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>BR-PAY-VNP-02</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Payments (VNPay)</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Cổng QR gói &amp; checkout</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Thanh toán QR demo cho gói seller và checkout buyer chỉ dùng VNPay (đã gỡ Postpay); method API initiate: VNPAY_QR.</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Buyer / Seller / System</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Checkout &amp; package checkout</v>
+      </c>
+      <c r="G111" t="str">
+        <v>Chọn QR thanh toán</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Backend/FE chỉ nhánh VNPAY_QR / provider VNPAY</v>
+      </c>
+      <c r="I111" t="str">
+        <v>MUST</v>
+      </c>
+      <c r="J111" t="str">
+        <v>docs/PAYMENTS-VNPAY.md; paymentController.js</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>BR-NOTIF-I18N-01</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Notifications</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Đa ngôn ngữ thông báo</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Thông báo in-app lưu titleKey/messageKey (và params) để hiển thị theo locale hiện tại; hỗ trợ map legacy chuỗi EN cũ.</v>
+      </c>
+      <c r="E112" t="str">
+        <v>System / FE</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Hiển thị NotificationsPage</v>
+      </c>
+      <c r="G112" t="str">
+        <v>Có hoặc không có key</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Ưu tiên t(key); fallback map legacy EN → key</v>
+      </c>
+      <c r="I112" t="str">
+        <v>SHOULD</v>
+      </c>
+      <c r="J112" t="str">
+        <v>notificationDisplay.ts; useNotificationStore</v>
       </c>
     </row>
   </sheetData>

--- a/ReBike_BusinessRules_Template.xlsx
+++ b/ReBike_BusinessRules_Template.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1011"/>
+  <dimension ref="A1:J1032"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4261,13 +4261,244 @@
         <v>notificationDisplay.ts; useNotificationStore</v>
       </c>
     </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v>BR-ORD-01</v>
+      </c>
+      <c r="B1012" t="str">
+        <v>fulfillmentType WAREHOUSE vs DIRECT</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>Order có fulfillmentType: WAREHOUSE (xe certified) hoặc DIRECT (xe unverified).</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v>BR-ORD-02</v>
+      </c>
+      <c r="B1013" t="str">
+        <v>Luồng WAREHOUSE</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>Xe tại kho → AT_WAREHOUSE_PENDING_ADMIN → admin confirm → SHIPPING (24h countdown).</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v>BR-ORD-03</v>
+      </c>
+      <c r="B1014" t="str">
+        <v>Luồng DIRECT</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>PENDING_SELLER_SHIP → seller ship-to-buyer → SHIPPING. Không qua kho.</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>BR-ORD-04</v>
+      </c>
+      <c r="B1015" t="str">
+        <v>Hủy đơn chỉ khi DIRECT</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>Buyer chỉ hủy được khi fulfillmentType=DIRECT. WAREHOUSE không cho hủy.</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>BR-ORD-05</v>
+      </c>
+      <c r="B1016" t="str">
+        <v>confirm-warehouse chỉ WAREHOUSE</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>Admin confirm-warehouse chỉ áp dụng đơn WAREHOUSE. DIRECT trả 400.</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>BR-ORD-06</v>
+      </c>
+      <c r="B1017" t="str">
+        <v>confirm-warehouse yêu cầu thanh toán</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>Yêu cầu depositPaid hoặc vnpayPaymentStatus=PAID mới confirm.</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>BR-ORD-07</v>
+      </c>
+      <c r="B1018" t="str">
+        <v>Query đơn chờ kho</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>WAREHOUSE_ONLY_FILTER: chỉ đơn fulfillmentType=WAREHOUSE.</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>BR-ORD-08</v>
+      </c>
+      <c r="B1019" t="str">
+        <v>Seller GET /orders</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>Hai nhánh: kho (SELLER_SHIPPED, AT_WAREHOUSE, không DIRECT); direct (PENDING_SELLER_SHIP + DIRECT).</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v>BR-ORD-09</v>
+      </c>
+      <c r="B1020" t="str">
+        <v>FIFO listing</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>Available → Reserved (sau deposit) → Sold. Cancel/Fail → Available.</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>BR-ORD-10</v>
+      </c>
+      <c r="B1021" t="str">
+        <v>Reserve khi deposit OK</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>Reserve chỉ tạo khi deposit payment thành công (24h countdown).</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>BR-PAY-VNP-01</v>
+      </c>
+      <c r="B1022" t="str">
+        <v>Chỉ VNPAY buyer checkout</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>Bỏ CASH/COD. POST /api/buyer/orders/vnpay-checkout (DEPOSIT 8% hoặc FULL).</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>BR-PAY-VNP-02</v>
+      </c>
+      <c r="B1023" t="str">
+        <v>Chỉ VNPAY gói seller</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>Gói đăng tin dùng VNPay (bỏ Postpay).</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>BR-PAY-VNP-03</v>
+      </c>
+      <c r="B1024" t="str">
+        <v>Deposit 8%</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>Deposit = 8% giá trị đơn. Đồng bộ FE và BE.</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>BR-PAY-VNP-04</v>
+      </c>
+      <c r="B1025" t="str">
+        <v>Return URL cập nhật depositPaid</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>IPN hoặc Return URL cập nhật depositPaid, vnpayPaymentStatus=PAID. Return URL cũng cập nhật khi IPN không gọi được (localhost).</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v>BR-PAY-VNP-05</v>
+      </c>
+      <c r="B1026" t="str">
+        <v>Finalize thanh toán số dư</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>Buyer thanh toán phần còn lại (khi chọn DEPOSIT) trước Complete.</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v>BR-FIN-01</v>
+      </c>
+      <c r="B1027" t="str">
+        <v>Lấy tin từ order.listing</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>Finalize ưu tiên lấy listing từ order.listing khi có orderId. Không phụ thuộc GET /bikes/:id.</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v>BR-FIN-02</v>
+      </c>
+      <c r="B1028" t="str">
+        <v>Bỏ form địa chỉ Finalize</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>Finalize không hiển thị form địa chỉ — buyer đã nhập ở checkout.</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v>BR-FIN-03</v>
+      </c>
+      <c r="B1029" t="str">
+        <v>GET /bikes/:id chỉ PUBLISHED</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>API chỉ trả PUBLISHED. RESERVED có thể 404. Finalize dùng order.listing.</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v>BR-TIME-01</v>
+      </c>
+      <c r="B1030" t="str">
+        <v>Countdown 24h khi SHIPPING</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>Hiển thị đếm ngược 24h từ expiresAt để buyer hoàn tất nhận hàng.</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v>BR-TIME-02</v>
+      </c>
+      <c r="B1031" t="str">
+        <v>Refetch khi chờ giao</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>Refetch đơn mỗi 5s khi chờ seller/kho xác nhận giao.</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>BR-TIME-03</v>
+      </c>
+      <c r="B1032" t="str">
+        <v>expiresAt khi chuyển SHIPPING</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>Set khi admin confirm (WAREHOUSE) hoặc seller ship-to-buyer (DIRECT).</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1011"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J1032"/>
   </ignoredErrors>
 </worksheet>
 </file>
